--- a/inputs/data_symbols_TD/14_LTAN06_800km_1213COLD_MY_STTLCT_PCDU_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/14_LTAN06_800km_1213COLD_MY_STTLCT_PCDU_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68D41DB0-9EAB-4DB1-A55E-A1B8593EA970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68409657-4F73-4298-9637-B842A24F2AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{CD0FB969-F8A8-4EEA-AE57-B62628A48045}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{1C257D7B-1042-4288-98E6-BE5819824545}"/>
   </bookViews>
   <sheets>
     <sheet name="14_LTAN06_800km_1213COLD_MY_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07ED241D-2C7C-44B4-96C8-063E8E0774AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FAB9C02-FDE6-4B11-BE33-B49DCCBFBF13}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>93.354920000000007</v>
+        <v>82.925160000000005</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>93.354920000000007</v>
+        <v>82.925160000000005</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>93.35521</v>
+        <v>82.925160000000005</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>93.356300000000005</v>
+        <v>82.925290000000004</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>93.358469999999997</v>
+        <v>82.925759999999997</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>93.361949999999993</v>
+        <v>82.926720000000003</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>93.366919999999993</v>
+        <v>82.928299999999993</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>93.373530000000002</v>
+        <v>82.930589999999995</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>93.381929999999997</v>
+        <v>82.933710000000005</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>93.392250000000004</v>
+        <v>82.937740000000005</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>93.404610000000005</v>
+        <v>82.942760000000007</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>93.419089999999997</v>
+        <v>82.948840000000004</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>93.435770000000005</v>
+        <v>82.956029999999998</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>93.454689999999999</v>
+        <v>82.964359999999999</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>93.475890000000007</v>
+        <v>82.973889999999997</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>93.499369999999999</v>
+        <v>82.984610000000004</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>93.525099999999995</v>
+        <v>82.996539999999996</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>93.553070000000005</v>
+        <v>83.009680000000003</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>93.583209999999994</v>
+        <v>83.024019999999993</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>93.611699999999999</v>
+        <v>83.037769999999995</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1311,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>93.634159999999994</v>
+        <v>83.048810000000003</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>93.649630000000002</v>
+        <v>83.056640000000002</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="D24">
-        <v>93.657420000000002</v>
+        <v>83.060860000000005</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1353,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>93.656840000000003</v>
+        <v>83.061059999999998</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>93.647270000000006</v>
+        <v>83.056849999999997</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -1381,7 +1381,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>93.628069999999994</v>
+        <v>83.047830000000005</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>93.598690000000005</v>
+        <v>83.033649999999994</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>93.55865</v>
+        <v>83.01397</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="D30">
-        <v>93.507589999999993</v>
+        <v>82.98854</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -1437,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>93.445260000000005</v>
+        <v>82.957130000000006</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
@@ -1451,7 +1451,7 @@
         <v>3</v>
       </c>
       <c r="D32">
-        <v>93.371520000000004</v>
+        <v>82.919610000000006</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>93.286370000000005</v>
+        <v>82.875900000000001</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -1479,7 +1479,7 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>93.189899999999994</v>
+        <v>82.825959999999995</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>93.082279999999997</v>
+        <v>82.769850000000005</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>92.963769999999997</v>
+        <v>82.707620000000006</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
@@ -1521,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>92.834689999999995</v>
+        <v>82.639390000000006</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>92.698530000000005</v>
+        <v>82.566909999999993</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>92.559229999999999</v>
+        <v>82.492199999999997</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>92.418180000000007</v>
+        <v>82.415909999999997</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>92.276610000000005</v>
+        <v>82.338669999999993</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>92.135729999999995</v>
+        <v>82.261080000000007</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>91.996719999999996</v>
+        <v>82.183769999999996</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>91.860759999999999</v>
+        <v>82.10736</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>91.728909999999999</v>
+        <v>82.032420000000002</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>91.602159999999998</v>
+        <v>81.959509999999995</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>91.481359999999995</v>
+        <v>81.889099999999999</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>91.367199999999997</v>
+        <v>81.821619999999996</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>91.260249999999999</v>
+        <v>81.757419999999996</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>91.160910000000001</v>
+        <v>81.696759999999998</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>91.069469999999995</v>
+        <v>81.639849999999996</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>90.986090000000004</v>
+        <v>81.586849999999998</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>90.910820000000001</v>
+        <v>81.537859999999995</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>90.843639999999994</v>
+        <v>81.492919999999998</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>90.784469999999999</v>
+        <v>81.452060000000003</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>90.733149999999995</v>
+        <v>81.415270000000007</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>90.689499999999995</v>
+        <v>81.38252</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>90.653300000000002</v>
+        <v>81.353759999999994</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>90.624300000000005</v>
+        <v>81.328940000000003</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>90.602239999999995</v>
+        <v>81.307969999999997</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>90.58681</v>
+        <v>81.290779999999998</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>90.577730000000003</v>
+        <v>81.277259999999998</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>90.574680000000001</v>
+        <v>81.267290000000003</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>90.577340000000007</v>
+        <v>81.260750000000002</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>90.585409999999996</v>
+        <v>81.25752</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>90.598550000000003</v>
+        <v>81.257440000000003</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>90.61645</v>
+        <v>81.260379999999998</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>90.638800000000003</v>
+        <v>81.266189999999995</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>90.665279999999996</v>
+        <v>81.274699999999996</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>90.695580000000007</v>
+        <v>81.285759999999996</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>90.729410000000001</v>
+        <v>81.299210000000002</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>90.766499999999994</v>
+        <v>81.314920000000001</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>90.806579999999997</v>
+        <v>81.332740000000001</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>90.84939</v>
+        <v>81.352509999999995</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>90.894660000000002</v>
+        <v>81.374049999999997</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>90.942149999999998</v>
+        <v>81.397220000000004</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>90.991619999999998</v>
+        <v>81.421859999999995</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>91.042829999999995</v>
+        <v>81.447829999999996</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>91.095590000000001</v>
+        <v>81.474999999999994</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>91.149699999999996</v>
+        <v>81.503219999999999</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>91.204980000000006</v>
+        <v>81.53237</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>91.261259999999993</v>
+        <v>81.56232</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>91.318380000000005</v>
+        <v>81.592969999999994</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>91.37621</v>
+        <v>81.624200000000002</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>91.43459</v>
+        <v>81.655929999999998</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>91.49342</v>
+        <v>81.688050000000004</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>91.552570000000003</v>
+        <v>81.720489999999998</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>91.611959999999996</v>
+        <v>81.75318</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>91.671490000000006</v>
+        <v>81.786060000000006</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>91.731099999999998</v>
+        <v>81.819050000000004</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>91.790729999999996</v>
+        <v>81.852109999999996</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>91.850319999999996</v>
+        <v>81.885189999999994</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>91.909850000000006</v>
+        <v>81.91825</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>91.969260000000006</v>
+        <v>81.951269999999994</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>92.028540000000007</v>
+        <v>81.984219999999993</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>92.08766</v>
+        <v>82.017080000000007</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>92.146619999999999</v>
+        <v>82.049840000000003</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>92.205410000000001</v>
+        <v>82.082490000000007</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>92.264039999999994</v>
+        <v>82.115030000000004</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>92.322500000000005</v>
+        <v>82.147459999999995</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>92.380809999999997</v>
+        <v>82.1798</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>92.438999999999993</v>
+        <v>82.212059999999994</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>92.497100000000003</v>
+        <v>82.24427</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>92.555120000000002</v>
+        <v>82.276449999999997</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>92.613100000000003</v>
+        <v>82.308629999999994</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>92.671059999999997</v>
+        <v>82.340810000000005</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>92.729029999999995</v>
+        <v>82.37303</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>92.787030000000001</v>
+        <v>82.40531</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>92.845089999999999</v>
+        <v>82.437650000000005</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>92.903210000000001</v>
+        <v>82.470079999999996</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>92.961429999999993</v>
+        <v>82.502610000000004</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>93.019760000000005</v>
+        <v>82.535259999999994</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>93.078220000000002</v>
+        <v>82.568049999999999</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>93.136840000000007</v>
+        <v>82.600980000000007</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>93.195639999999997</v>
+        <v>82.634060000000005</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>93.254630000000006</v>
+        <v>82.667299999999997</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>93.313829999999996</v>
+        <v>82.700720000000004</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>93.373249999999999</v>
+        <v>82.734319999999997</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>93.43289</v>
+        <v>82.768100000000004</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>93.492779999999996</v>
+        <v>82.802070000000001</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
@@ -2697,7 +2697,7 @@
         <v>3</v>
       </c>
       <c r="D121">
-        <v>93.54907</v>
+        <v>82.834450000000004</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
@@ -2711,7 +2711,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>93.597449999999995</v>
+        <v>82.863119999999995</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="D123">
-        <v>93.637020000000007</v>
+        <v>82.887619999999998</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="D124">
-        <v>93.667169999999999</v>
+        <v>82.907560000000004</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
@@ -2753,7 +2753,7 @@
         <v>3</v>
       </c>
       <c r="D125">
-        <v>93.68732</v>
+        <v>82.922600000000003</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="D126">
-        <v>93.696920000000006</v>
+        <v>82.93235</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
@@ -2781,7 +2781,7 @@
         <v>3</v>
       </c>
       <c r="D127">
-        <v>93.695430000000002</v>
+        <v>82.936480000000003</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
@@ -2795,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="D128">
-        <v>93.682379999999995</v>
+        <v>82.934650000000005</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
@@ -2809,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>93.657380000000003</v>
+        <v>82.926580000000001</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
@@ -2823,7 +2823,7 @@
         <v>3</v>
       </c>
       <c r="D130">
-        <v>93.620140000000006</v>
+        <v>82.912040000000005</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
@@ -2837,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="D131">
-        <v>93.570509999999999</v>
+        <v>82.890860000000004</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
@@ -2851,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="D132">
-        <v>93.508439999999993</v>
+        <v>82.862920000000003</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
@@ -2865,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>93.433970000000002</v>
+        <v>82.828180000000003</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
@@ -2879,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="D134">
-        <v>93.347269999999995</v>
+        <v>82.786659999999998</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
@@ -2893,7 +2893,7 @@
         <v>3</v>
       </c>
       <c r="D135">
-        <v>93.248580000000004</v>
+        <v>82.738420000000005</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="D136">
-        <v>93.138229999999993</v>
+        <v>82.68356</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
@@ -2921,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="D137">
-        <v>93.016589999999994</v>
+        <v>82.622230000000002</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>92.887219999999999</v>
+        <v>82.556200000000004</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>92.75412</v>
+        <v>82.487520000000004</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>92.618729999999999</v>
+        <v>82.416889999999995</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>92.482330000000005</v>
+        <v>82.344949999999997</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>92.346170000000001</v>
+        <v>82.272329999999997</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>92.211460000000002</v>
+        <v>82.199659999999994</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>92.079400000000007</v>
+        <v>82.127600000000001</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>91.951099999999997</v>
+        <v>82.056730000000002</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>91.827569999999994</v>
+        <v>81.987620000000007</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>91.709670000000003</v>
+        <v>81.920779999999993</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>91.598129999999998</v>
+        <v>81.856629999999996</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>91.493530000000007</v>
+        <v>81.795540000000003</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>91.396299999999997</v>
+        <v>81.737780000000001</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>91.306719999999999</v>
+        <v>81.683599999999998</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>91.224990000000005</v>
+        <v>81.633129999999994</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>91.151169999999993</v>
+        <v>81.586500000000001</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>91.085260000000005</v>
+        <v>81.543769999999995</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>91.027180000000001</v>
+        <v>81.504959999999997</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>90.976780000000005</v>
+        <v>81.470079999999996</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>90.933899999999994</v>
+        <v>81.439099999999996</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>90.898319999999998</v>
+        <v>81.412000000000006</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>90.869820000000004</v>
+        <v>81.388710000000003</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>90.848119999999994</v>
+        <v>81.369169999999997</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>90.832939999999994</v>
+        <v>81.353290000000001</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>90.823999999999998</v>
+        <v>81.340990000000005</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>90.820989999999995</v>
+        <v>81.332139999999995</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>90.823599999999999</v>
+        <v>81.326650000000001</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>90.831519999999998</v>
+        <v>81.324370000000002</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>90.844440000000006</v>
+        <v>81.32517</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>90.862049999999996</v>
+        <v>81.328919999999997</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>90.884029999999996</v>
+        <v>81.335470000000001</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="D169">
-        <v>90.910079999999994</v>
+        <v>81.344660000000005</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>90.939890000000005</v>
+        <v>81.35633</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>90.973169999999996</v>
+        <v>81.370339999999999</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>91.009659999999997</v>
+        <v>81.386560000000003</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>91.049090000000007</v>
+        <v>81.404839999999993</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>91.091210000000004</v>
+        <v>81.42501</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="D175">
-        <v>91.135750000000002</v>
+        <v>81.446920000000006</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>91.182479999999998</v>
+        <v>81.470410000000001</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>91.231139999999996</v>
+        <v>81.495339999999999</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>91.28152</v>
+        <v>81.521559999999994</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>91.333420000000004</v>
+        <v>81.548950000000005</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>91.38664</v>
+        <v>81.577359999999999</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>91.441010000000006</v>
+        <v>81.606660000000005</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>91.496359999999996</v>
+        <v>81.636740000000003</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>91.552530000000004</v>
+        <v>81.667490000000001</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>91.609390000000005</v>
+        <v>81.698800000000006</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>91.666790000000006</v>
+        <v>81.730580000000003</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>91.724609999999998</v>
+        <v>81.762739999999994</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>91.782759999999996</v>
+        <v>81.795190000000005</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>91.841130000000007</v>
+        <v>81.827879999999993</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>91.899630000000002</v>
+        <v>81.860730000000004</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>91.958200000000005</v>
+        <v>81.893680000000003</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>92.016779999999997</v>
+        <v>81.926680000000005</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>92.075320000000005</v>
+        <v>81.959689999999995</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>92.133790000000005</v>
+        <v>81.992670000000004</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>92.192139999999995</v>
+        <v>82.025599999999997</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>92.250349999999997</v>
+        <v>82.058440000000004</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="D196">
-        <v>92.308400000000006</v>
+        <v>82.091189999999997</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>92.366290000000006</v>
+        <v>82.123819999999995</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>92.424009999999996</v>
+        <v>82.15634</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>92.481549999999999</v>
+        <v>82.188730000000007</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>92.538939999999997</v>
+        <v>82.221010000000007</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>92.596180000000004</v>
+        <v>82.253190000000004</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>92.653300000000002</v>
+        <v>82.28528</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="D203">
-        <v>92.710319999999996</v>
+        <v>82.317319999999995</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>92.767269999999996</v>
+        <v>82.349320000000006</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>92.824179999999998</v>
+        <v>82.381309999999999</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>92.881069999999994</v>
+        <v>82.413309999999996</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>92.937979999999996</v>
+        <v>82.445329999999998</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>92.994919999999993</v>
+        <v>82.477400000000003</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>93.051910000000007</v>
+        <v>82.509540000000001</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>93.108980000000003</v>
+        <v>82.541759999999996</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="D211">
-        <v>93.166139999999999</v>
+        <v>82.574089999999998</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>93.223420000000004</v>
+        <v>82.606530000000006</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.4">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="D213">
-        <v>93.280839999999998</v>
+        <v>82.639099999999999</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="D214">
-        <v>93.338409999999996</v>
+        <v>82.671809999999994</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="D215">
-        <v>93.396169999999998</v>
+        <v>82.704669999999993</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="D216">
-        <v>93.454120000000003</v>
+        <v>82.737690000000001</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>93.512289999999993</v>
+        <v>82.770880000000005</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="D218">
-        <v>93.570679999999996</v>
+        <v>82.804249999999996</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D219">
-        <v>93.629310000000004</v>
+        <v>82.837800000000001</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="D220">
-        <v>93.68817</v>
+        <v>82.871539999999996</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
@@ -4097,7 +4097,7 @@
         <v>3</v>
       </c>
       <c r="D221">
-        <v>93.743449999999996</v>
+        <v>82.903679999999994</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>3</v>
       </c>
       <c r="D222">
-        <v>93.790800000000004</v>
+        <v>82.932119999999998</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.4">
@@ -4125,7 +4125,7 @@
         <v>3</v>
       </c>
       <c r="D223">
-        <v>93.829359999999994</v>
+        <v>82.956379999999996</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.4">
@@ -4139,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="D224">
-        <v>93.85848</v>
+        <v>82.976089999999999</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.4">
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="D225">
-        <v>93.877589999999998</v>
+        <v>82.990870000000001</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.4">
@@ -4167,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>93.886150000000001</v>
+        <v>83.000380000000007</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.4">
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="D227">
-        <v>93.883619999999993</v>
+        <v>83.004260000000002</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.4">
@@ -4195,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="D228">
-        <v>93.869529999999997</v>
+        <v>83.002179999999996</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.4">
@@ -4209,7 +4209,7 @@
         <v>3</v>
       </c>
       <c r="D229">
-        <v>93.84348</v>
+        <v>82.993849999999995</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.4">
@@ -4223,7 +4223,7 @@
         <v>3</v>
       </c>
       <c r="D230">
-        <v>93.805210000000002</v>
+        <v>82.979050000000001</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.4">
@@ -4237,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>93.754540000000006</v>
+        <v>82.957610000000003</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.4">
@@ -4251,7 +4251,7 @@
         <v>3</v>
       </c>
       <c r="D232">
-        <v>93.691419999999994</v>
+        <v>82.929410000000004</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.4">
@@ -4265,7 +4265,7 @@
         <v>3</v>
       </c>
       <c r="D233">
-        <v>93.61591</v>
+        <v>82.894409999999993</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.4">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D234">
-        <v>93.528180000000006</v>
+        <v>82.852630000000005</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.4">
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="D235">
-        <v>93.428470000000004</v>
+        <v>82.804130000000001</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.4">
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>93.317089999999993</v>
+        <v>82.748999999999995</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.4">
@@ -4321,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="D237">
-        <v>93.19444</v>
+        <v>82.68741</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.4">
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>93.064059999999998</v>
+        <v>82.621120000000005</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.4">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="D239">
-        <v>92.929969999999997</v>
+        <v>82.552180000000007</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="D240">
-        <v>92.793610000000001</v>
+        <v>82.481300000000005</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.4">
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="D241">
-        <v>92.65625</v>
+        <v>82.409099999999995</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.4">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="D242">
-        <v>92.519149999999996</v>
+        <v>82.336219999999997</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.4">
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="D243">
-        <v>92.383510000000001</v>
+        <v>82.263310000000004</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="D244">
-        <v>92.250550000000004</v>
+        <v>82.191000000000003</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.4">
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="D245">
-        <v>92.121350000000007</v>
+        <v>82.119889999999998</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.4">
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="D246">
-        <v>91.996939999999995</v>
+        <v>82.050539999999998</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.4">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>91.87818</v>
+        <v>81.983459999999994</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D248">
-        <v>91.765799999999999</v>
+        <v>81.919079999999994</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.4">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>91.660359999999997</v>
+        <v>81.857749999999996</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.4">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="D250">
-        <v>91.562309999999997</v>
+        <v>81.799769999999995</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.4">
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>91.471919999999997</v>
+        <v>81.745360000000005</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.4">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="D252">
-        <v>91.389390000000006</v>
+        <v>81.694670000000002</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.4">
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="D253">
-        <v>91.314779999999999</v>
+        <v>81.647819999999996</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.4">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>91.248080000000002</v>
+        <v>81.604860000000002</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.4">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>91.189220000000006</v>
+        <v>81.565839999999994</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.4">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>91.138050000000007</v>
+        <v>81.530739999999994</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.4">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>91.094409999999996</v>
+        <v>81.499539999999996</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.4">
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>91.058070000000001</v>
+        <v>81.472219999999993</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.4">
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>91.028819999999996</v>
+        <v>81.448719999999994</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.4">
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>91.006370000000004</v>
+        <v>81.428970000000007</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.4">
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>90.990449999999996</v>
+        <v>81.412880000000001</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.4">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="D262">
-        <v>90.980770000000007</v>
+        <v>81.400360000000006</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.4">
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="D263">
-        <v>90.977019999999996</v>
+        <v>81.391310000000004</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.4">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="D264">
-        <v>90.978890000000007</v>
+        <v>81.38561</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.4">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="D265">
-        <v>90.986080000000001</v>
+        <v>81.383120000000005</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.4">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="D266">
-        <v>90.998270000000005</v>
+        <v>81.383719999999997</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.4">
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="D267">
-        <v>91.015140000000002</v>
+        <v>81.387259999999998</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.4">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="D268">
-        <v>91.0364</v>
+        <v>81.393600000000006</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.4">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="D269">
-        <v>91.061719999999994</v>
+        <v>81.40258</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.4">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="D270">
-        <v>91.090810000000005</v>
+        <v>81.41404</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.4">
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>91.123369999999994</v>
+        <v>81.427850000000007</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.4">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="D272">
-        <v>91.159139999999994</v>
+        <v>81.443860000000001</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="D273">
-        <v>91.197850000000003</v>
+        <v>81.461939999999998</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.4">
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="D274">
-        <v>91.239249999999998</v>
+        <v>81.481909999999999</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.4">
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="D275">
-        <v>91.283079999999998</v>
+        <v>81.503609999999995</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.4">
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="D276">
-        <v>91.329089999999994</v>
+        <v>81.526899999999998</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="D277">
-        <v>91.377039999999994</v>
+        <v>81.55162</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.4">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="D278">
-        <v>91.42671</v>
+        <v>81.577650000000006</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.4">
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D279">
-        <v>91.477900000000005</v>
+        <v>81.604830000000007</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.4">
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="D280">
-        <v>91.530410000000003</v>
+        <v>81.633030000000005</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="D281">
-        <v>91.584069999999997</v>
+        <v>81.662130000000005</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.4">
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="D282">
-        <v>91.638720000000006</v>
+        <v>81.692009999999996</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.4">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="D283">
-        <v>91.694190000000006</v>
+        <v>81.722560000000001</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.4">
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>91.750339999999994</v>
+        <v>81.75367</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="D285">
-        <v>91.807040000000001</v>
+        <v>81.785250000000005</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.4">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D286">
-        <v>91.864170000000001</v>
+        <v>81.8172</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.4">
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="D287">
-        <v>91.921620000000004</v>
+        <v>81.849450000000004</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.4">
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="D288">
-        <v>91.979290000000006</v>
+        <v>81.88194</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.4">
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="D289">
-        <v>92.037099999999995</v>
+        <v>81.914590000000004</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.4">
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>92.094980000000007</v>
+        <v>81.947339999999997</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.4">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="D291">
-        <v>92.152869999999993</v>
+        <v>81.980140000000006</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.4">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>92.210729999999998</v>
+        <v>82.012950000000004</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.4">
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="D293">
-        <v>92.268510000000006</v>
+        <v>82.045739999999995</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.4">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="D294">
-        <v>92.326179999999994</v>
+        <v>82.078460000000007</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.4">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="D295">
-        <v>92.383719999999997</v>
+        <v>82.111109999999996</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.4">
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D296">
-        <v>92.441090000000003</v>
+        <v>82.143659999999997</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.4">
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="D297">
-        <v>92.498310000000004</v>
+        <v>82.176100000000005</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.4">
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>92.555359999999993</v>
+        <v>82.208410000000001</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.4">
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>92.61224</v>
+        <v>82.240610000000004</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="D300">
-        <v>92.668959999999998</v>
+        <v>82.272689999999997</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.4">
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="D301">
-        <v>92.725539999999995</v>
+        <v>82.304670000000002</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.4">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="D302">
-        <v>92.781989999999993</v>
+        <v>82.336569999999995</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.4">
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="D303">
-        <v>92.838350000000005</v>
+        <v>82.368409999999997</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_symbols_TD/14_LTAN06_800km_1213COLD_MY_STTLCT_PCDU_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/14_LTAN06_800km_1213COLD_MY_STTLCT_PCDU_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68409657-4F73-4298-9637-B842A24F2AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B315DB21-6EA3-4CD0-990E-3AF8F4BDD78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{1C257D7B-1042-4288-98E6-BE5819824545}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C4BA2FC3-472F-4D05-A7F8-42A920F3AD6A}"/>
   </bookViews>
   <sheets>
     <sheet name="14_LTAN06_800km_1213COLD_MY_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FAB9C02-FDE6-4B11-BE33-B49DCCBFBF13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE7918F9-77A0-47D9-9E1C-F11BB52900B5}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/14_LTAN06_800km_1213COLD_MY_STTLCT_PCDU_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/14_LTAN06_800km_1213COLD_MY_STTLCT_PCDU_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B315DB21-6EA3-4CD0-990E-3AF8F4BDD78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6608D7C2-A1E8-4DF8-A412-F66A51949463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C4BA2FC3-472F-4D05-A7F8-42A920F3AD6A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{6C1DC97E-2EDE-46C8-A33F-2377488E684B}"/>
   </bookViews>
   <sheets>
     <sheet name="14_LTAN06_800km_1213COLD_MY_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE7918F9-77A0-47D9-9E1C-F11BB52900B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1885B650-2E98-4374-96CC-D97D4667A6E7}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
